--- a/datasets/matrix_cca.xlsx
+++ b/datasets/matrix_cca.xlsx
@@ -493,7 +493,7 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>9.090909090909092</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>16.66666666666666</v>
+        <v>0</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>16.66666666666666</v>
+        <v>20</v>
       </c>
       <c r="O18">
         <v>0</v>
